--- a/lcr_analyses/clustering/carriers/AlcoR/cluster_summaries_hierarchical.xlsx
+++ b/lcr_analyses/clustering/carriers/AlcoR/cluster_summaries_hierarchical.xlsx
@@ -12,6 +12,10 @@
     <sheet name="k4" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="k5" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="k6" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="k7" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="k8" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="k9" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="k10" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4334,4 +4338,5520 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2206235011990408</v>
+      </c>
+      <c r="E2" t="n">
+        <v>49.33333333333334</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.2588235294117647</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.0449438202247191</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8352941176470589</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.3285302593659942</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.4927953890489913</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.2705882352941176</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1598360655737705</v>
+      </c>
+      <c r="E3" t="n">
+        <v>14.83333333333333</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5144927536231884</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.1797752808988764</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.4719101123595505</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1794871794871795</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.05797101449275362</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.2051282051282051</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.1123595505617977</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1014492753623188</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>938</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.294684298717078</v>
+      </c>
+      <c r="E4" t="n">
+        <v>62.3125</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1908315565031983</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5575692963752665</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1886993603411514</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.08208955223880597</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3411513859275053</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.04371002132196162</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.04051172707889126</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.04477611940298507</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.05543710021321962</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.08208955223880597</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1257995735607676</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1929637526652452</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.002132196162046908</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.08742004264392324</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.6727078891257996</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.220682302771855</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.152452025586354</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.003198294243070362</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.001066098081023454</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.02025586353944563</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.1908315565031983</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.5264750647524277</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.5951209401247251</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.2904796124156795</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.09831554799463862</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.5321369172165888</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1310283159463488</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1199662162162162</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2557054842068726</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.005401279583065943</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1374357764020261</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>362</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>39</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>247</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>81</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>52</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>63</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>52</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5193812526826691</v>
+      </c>
+      <c r="E5" t="n">
+        <v>43.71428571428572</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6096795352323838</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4921101949025487</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.1752529985007496</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.1013212143928036</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.6641210644677662</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1848669415292354</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1156859070464768</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.3005528485757122</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.06918103448275861</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.2804347826086956</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3978349120433017</v>
+      </c>
+      <c r="E6" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.5525672371638142</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.6140776699029126</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.2909535452322738</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.1059190031152648</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.1370716510903427</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1383495145631068</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.2597087378640777</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.01020408163265307</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1224489795918367</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3760939551595128</v>
+      </c>
+      <c r="E7" t="n">
+        <v>37.28571428571428</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.6425000000000001</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5009883720930233</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1943554294085333</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.06750137337483977</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.572617194652994</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1681201550387597</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.2659302325581395</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.4411337209302326</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.09072674418604651</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1295206921809192</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.07739938080495357</v>
+      </c>
+      <c r="E8" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.03200000000000001</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2206235011990408</v>
+      </c>
+      <c r="E2" t="n">
+        <v>49.33333333333334</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.2588235294117647</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.0449438202247191</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8352941176470589</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.3285302593659942</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.4927953890489913</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.2705882352941176</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1598360655737705</v>
+      </c>
+      <c r="E3" t="n">
+        <v>14.83333333333333</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5144927536231884</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.1797752808988764</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.4719101123595505</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1794871794871795</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.05797101449275362</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.2051282051282051</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.1123595505617977</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1014492753623188</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2184707050645482</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28.375</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.524904214559387</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.5965665236051502</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.3111111111111111</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.09595959595959594</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.4977973568281938</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1277533039647577</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2473118279569892</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.01515151515151516</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1328125</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>917</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2985074626865671</v>
+      </c>
+      <c r="E5" t="n">
+        <v>65</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1952017448200654</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5605234460196292</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.193020719738277</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.08287895310796074</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3358778625954199</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.04362050163576881</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.03925845147219193</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.04471101417666303</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.04907306434023991</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.08178844056706652</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1123227917121047</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1908396946564886</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.002181025081788441</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0752453653217012</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.6673936750272628</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.2137404580152672</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.148309705561614</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.002181025081788441</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.00109051254089422</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.01635768811341331</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.1744820065430752</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.5265017667844523</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.595003785011355</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.2898799313893654</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.09836065573770492</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.5323076923076923</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1313725490196078</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1194029850746269</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.2560975609756098</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.00564681724845996</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1379310344827586</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>354</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>238</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>51</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>62</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>52</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5193812526826691</v>
+      </c>
+      <c r="E6" t="n">
+        <v>43.71428571428572</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6096795352323838</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.4921101949025487</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1752529985007496</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.1013212143928036</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.6641210644677662</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.1848669415292354</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1156859070464768</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.3005528485757122</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.06918103448275861</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.2804347826086956</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3978349120433017</v>
+      </c>
+      <c r="E7" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5525672371638142</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.6140776699029126</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.2909535452322738</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.1059190031152648</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1370716510903427</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1383495145631068</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.2597087378640777</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.01020408163265307</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1224489795918367</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3760939551595128</v>
+      </c>
+      <c r="E8" t="n">
+        <v>37.28571428571428</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.6425000000000001</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.5009883720930233</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.1943554294085333</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.06750137337483977</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.572617194652994</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1681201550387597</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.2659302325581395</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.4411337209302326</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.09072674418604651</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1295206921809192</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.07739938080495357</v>
+      </c>
+      <c r="E9" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.03200000000000001</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2206235011990408</v>
+      </c>
+      <c r="E2" t="n">
+        <v>49.33333333333334</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.2588235294117647</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.0449438202247191</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8352941176470589</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.3285302593659942</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.4927953890489913</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.2705882352941176</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1598360655737705</v>
+      </c>
+      <c r="E3" t="n">
+        <v>14.83333333333333</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5144927536231884</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.1797752808988764</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.4719101123595505</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1794871794871795</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.05797101449275362</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.2051282051282051</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.1123595505617977</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1014492753623188</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2184707050645482</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28.375</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.524904214559387</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.5965665236051502</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.3111111111111111</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.09595959595959594</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.4977973568281938</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1277533039647577</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2473118279569892</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.01515151515151516</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1328125</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5101214574898786</v>
+      </c>
+      <c r="E5" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.5642458100558659</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.03968253968253968</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.6056074766355141</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1117647058823529</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1245136186770428</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.2264705882352941</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.02334630350194553</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1981308411214953</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>912</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2968434675791875</v>
+      </c>
+      <c r="E6" t="n">
+        <v>65</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1951754385964912</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5603070175438597</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.194078947368421</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.04385964912280702</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.03947368421052631</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.04385964912280702</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0493421052631579</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.07785087719298246</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1129385964912281</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1896929824561404</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.002192982456140351</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.07456140350877193</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.6710526315789473</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.2094298245614035</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1469298245614035</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.002192982456140351</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.001096491228070175</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.01535087719298246</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.1721491228070176</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.5265705555233737</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5952885391444713</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.290164425409566</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.09840929122955309</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.5322109036030938</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.1314757481940144</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1194029850746269</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.2562539086929331</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.005847953216374269</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1371939362673122</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>352</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>238</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>79</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>62</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>52</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5193812526826691</v>
+      </c>
+      <c r="E7" t="n">
+        <v>43.71428571428572</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.6096795352323838</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.4921101949025487</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1752529985007496</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.1013212143928036</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.6641210644677662</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1848669415292354</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1156859070464768</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.3005528485757122</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.06918103448275861</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.2804347826086956</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3978349120433017</v>
+      </c>
+      <c r="E8" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.5525672371638142</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.6140776699029126</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.2909535452322738</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.1059190031152648</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1370716510903427</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1383495145631068</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.2597087378640777</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.01020408163265307</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1224489795918367</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3760939551595128</v>
+      </c>
+      <c r="E9" t="n">
+        <v>37.28571428571428</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.6425000000000001</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.5009883720930233</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.1943554294085333</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.06750137337483977</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.572617194652994</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.1681201550387597</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.2659302325581395</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.4411337209302326</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.09072674418604651</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1295206921809192</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>15</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.07739938080495357</v>
+      </c>
+      <c r="E10" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.03200000000000001</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2206235011990408</v>
+      </c>
+      <c r="E2" t="n">
+        <v>49.33333333333334</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.2588235294117647</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.0449438202247191</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8352941176470589</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.3285302593659942</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.4927953890489913</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.2705882352941176</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1598360655737705</v>
+      </c>
+      <c r="E3" t="n">
+        <v>14.83333333333333</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5144927536231884</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.1797752808988764</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.4719101123595505</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1794871794871795</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.05797101449275362</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.2051282051282051</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.1123595505617977</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1014492753623188</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2184707050645482</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28.375</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.524904214559387</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.5965665236051502</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.3111111111111111</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.09595959595959594</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.4977973568281938</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1277533039647577</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2473118279569892</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.01515151515151516</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1328125</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5101214574898786</v>
+      </c>
+      <c r="E5" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.5642458100558659</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.03968253968253968</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.6056074766355141</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1117647058823529</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1245136186770428</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.2264705882352941</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.02334630350194553</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1981308411214953</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>105</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4127659574468085</v>
+      </c>
+      <c r="E6" t="n">
+        <v>33.33333333333334</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6761904761904762</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2476190476190476</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.009523809523809525</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.08571428571428572</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.2571428571428571</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.2761904761904762</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4952380952380953</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.3047619047619048</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.4857142857142857</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.5250783699059561</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5936395759717314</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.3061630218687873</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.0964722822174226</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.5321100917431193</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.1333333333333334</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1225296442687747</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.265017667844523</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.005154639175257732</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1318051575931232</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>33</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>807</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="E7" t="n">
+        <v>73</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1338289962825279</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5142503097893433</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.1313506815365551</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.06195786864931847</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.2775712515489467</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0483271375464684</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.03841387856257745</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.04337050805452292</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.04460966542750929</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.05452292441140025</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.09169764560099132</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1499380421313507</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.002478314745972739</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.04460966542750929</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.6431226765799256</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1871127633209418</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.114002478314746</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.002478314745972739</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.001239157372986369</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.01115241635687732</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1313506815365551</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.527363184079602</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5953389830508474</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.2892561983471074</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.09900990099009901</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.532258064516129</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1307550644567219</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1184834123222749</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.2555205047318612</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.005847953216374269</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1388367729831144</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>319</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>37</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>68</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>51</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5193812526826691</v>
+      </c>
+      <c r="E8" t="n">
+        <v>43.71428571428572</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.6096795352323838</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.4921101949025487</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.1752529985007496</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.1013212143928036</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.6641210644677662</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1848669415292354</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1156859070464768</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.3005528485757122</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.06918103448275861</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2804347826086956</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3978349120433017</v>
+      </c>
+      <c r="E9" t="n">
+        <v>25.375</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.5525672371638142</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.6140776699029126</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.2909535452322738</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.1059190031152648</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.1370716510903427</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.1383495145631068</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.2597087378640777</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.01020408163265307</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1224489795918367</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3760939551595128</v>
+      </c>
+      <c r="E10" t="n">
+        <v>37.28571428571428</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.6425000000000001</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.5009883720930233</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.1943554294085333</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.06750137337483977</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.572617194652994</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.1681201550387597</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.2659302325581395</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.4411337209302326</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.09072674418604651</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.1295206921809192</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.07739938080495357</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.03200000000000001</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>